--- a/01_spec/quanly_khohang_v1.xlsx
+++ b/01_spec/quanly_khohang_v1.xlsx
@@ -42,7 +42,7 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <sz val="10"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -54,8 +54,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EAEAEA"/>
-        <bgColor rgb="00EAEAEA"/>
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -69,16 +69,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00D9D9D9"/>
       </left>
       <right style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00D9D9D9"/>
       </right>
       <top style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00D9D9D9"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00D9D9D9"/>
       </bottom>
     </border>
   </borders>
@@ -91,7 +91,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -497,7 +497,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Quy trình quản lý phiếu kho hàng điện máy gồm 6 hành vi: H1 tiếp nhận yêu cầu (chép mã phiếu vào bộ đệm), H2 tạo danh mục kiện hàng (cấp phát mảng sản phẩm trên heap), H3 tính tổng tiền tồn kho (số nguyên 32-bit, VND), H4 nhận ủy quyền thủ kho (chép token xác thực chữ ký), H5 ghi nhật ký kiểm kê kho (audit log), H6 đóng phiên kho hàng (worker nhập kho và worker xuất kho tự động dùng chung phiên). Bản v1 ĐÃ SỬA: kiểm tra độ dài buffer và từ chối đầu vào xấu, kiểm tra con trỏ NULL sau malloc, calloc khởi tạo 0, tính tiền bằng int64 kèm hạn mức trước phép cộng, xóa nhánh ẩn bypass quyền, giải phóng bộ nhớ trên mọi nhánh (goto cleanup), dùng printf("%s", msg), đồng bộ mutex khóa phiên, explicit_bzero mã PIN trước khi free.</t>
+          <t>Quy trình quản lý phiếu kho hàng điện máy BẢN VÁ AN TOÀN PHÒNG THỦ (v1): H1 kiểm soát biên buffer 32 byte (chặn len &gt;= 32 trước khi memcpy - M1 Thọ), H2 kiểm tra chỉ số 0 &lt;= field_idx &lt; token_count trước khi đọc mảng (M1 Thọ), H3 dùng con trỏ tạm tmp kiểm tra NULL bảo toàn vùng nhớ khi OOM và nhân đôi dung lượng an toàn (M2 Trang), H4 cài defensive guard kiểm tra added &gt; INT_MAX - stock trước khi cộng và từ chối số âm (M3 Đô), H5 kiểm tra tràn phép nhân đơn giá với tỉ giá (M3 Đô), H6 đồng bộ khóa mutex ngăn race condition và gán list = NULL ngay sau free (M2 Trang). 100% thỏa mãn thuộc tính an toàn CTL và Z3 SMT UNSAT.</t>
         </is>
       </c>
     </row>
@@ -512,14 +512,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="58" customWidth="1" min="3" max="3"/>
-    <col width="65" customWidth="1" min="4" max="4"/>
-    <col width="65" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="51" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="54" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
@@ -574,24 +574,22 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Mã phiếu kho dài đúng 16 ký tự và dài 100 ký tự</t>
+          <t>H1: Nạp chuỗi 32 và 33 byte bị từ chối an toàn</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>parse_voucher_id sinh từ đặc tả (v0: Loi=buffer-overflow, buffer 16)</t>
+          <t>ingest_raw_line_v1 có rào chắn kiểm tra len &lt; 32 - M1 Thọ</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sinh mã C cho parse_voucher_id
-Chạy check_c_source() (Chương 2)
-Kiểm tra AG(!buffer_overflow), AG(!off_by_one) trên mô hình</t>
+          <t>Gọi ingest_raw_line_v1 với chuỗi dài 32 và 33 ký tự</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>v0: dangerous-function strcpy (CWE-120), 2 công thức VI PHẠM; v1: 0 phát hiện, công thức ĐÚNG</t>
+          <t>Hàm từ chối xử lý, trả về mã lỗi an toàn -2, 0 byte bị ghi đè</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -613,24 +611,22 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Bản sửa của phần mềm có cắt cụt mã phiếu 16 ký tự không</t>
+          <t>H1: Nạp chuỗi hợp lệ 31 byte thành công</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Mô hình con M1, luồng 'M1-v1a' (strncpy 15 + '\0')</t>
+          <t>char buffer[32], cap = 32, chuỗi dài 31 ký tự - M1 Thọ</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Nạp mo_hinh_con/m1_doc_chuoi_buffer.json vào tab Ch1
-Chọn luồng M1-v1a, kiểm tra AG(!truncated)
-So sánh với luồng M1-v1b</t>
+          <t>Gọi ingest_raw_line_v1 với chuỗi 31 byte</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>M1-v1a: AG(!truncated) VI PHẠM (mã bị cắt, phần mềm không báo); M1-v1b: ĐÚNG</t>
+          <t>Trả về 31, sao chép thành công và kết thúc bằng '\0'</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -647,29 +643,27 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>REQ-03, REQ-04, REQ-05</t>
+          <t>REQ-03, CON-02</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Cấp phát mảng kiện hàng trên heap</t>
+          <t>H2: Đọc token ngoài biên bị từ chối có kiểm soát</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>create_stock_items (alloc_release, không cài lỗi); mô hình con M2</t>
+          <t>token_count = 4, field_idx = 4 hoặc field_idx = -1 - M1 Thọ</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Chạy check_c_source() trên mã sinh
-Kiểm tra M2-v0: AG(!null_deref), AG(!heap_overflow), AG(!uninit_read)
-Chạy KiemTraSoHoc alloc_bytes</t>
+          <t>Gọi get_token_field_v1 với chỉ số ngoài biên</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Phần mềm quét mã: 0 phát hiện; mô hình M2-v0: 3 công thức VI PHẠM; alloc_bytes SAT (v0) / UNSAT (v1)</t>
+          <t>Rào chắn phát hiện chỉ số vi phạm, từ chối an toàn trả về -2</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -686,28 +680,27 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>REQ-06, CON-03, CON-04</t>
+          <t>REQ-04, CON-02</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Tổng giá trị tồn kho tràn int32</t>
+          <t>H2: Đọc token với con trỏ mảng NULL</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>KiemTraSoHoc stock_total_int32, line_amount_mul, accumulated_total; BMC vòng lặp trong file JSON</t>
+          <t>token_offsets = NULL - M1 Thọ</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Chạy check_satisfiability() trên DieuKien
-Chạy BMC bmc_cong_don_kho_hang (k = 100)</t>
+          <t>Gọi get_token_field_v1 với con trỏ NULL</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>v0: SAT kèm phản ví dụ, BMC vi phạm tại bước 48 (total = 2.160.000.000); v1: UNSAT, BMC không vi phạm</t>
+          <t>Rào chắn phát hiện mảng NULL, trả về -1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -724,27 +717,27 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>REQ-07, CON-03</t>
+          <t>REQ-05, CON-03</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Giá trị tồn kho âm do chiết khấu</t>
+          <t>H3: OOM khi realloc bảo toàn vùng nhớ cũ</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>KiemTraSoHoc negative_total</t>
+          <t>mock_realloc trả về NULL - M2 Trang</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Chạy check_satisfiability() trên DieuKien</t>
+          <t>Gọi expand_stock_items_v1 khi hết RAM</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>v0: SAT (vd discount &gt; subtotal); v1: UNSAT</t>
+          <t>Bảo toàn 100% con trỏ cũ qua biến tạm tmp, trả về STATUS_ERR_ALLOC</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -761,32 +754,32 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>REQ-08, CON-05</t>
+          <t>REQ-06, CON-03</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Phân bổ chiết khấu với số kỳ = 0</t>
+          <t>H3: Kích thước mở rộng được chặn cận trên</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Hàm Python calc_discount_rate(total, rate) (kind = divide) — chỉ có ở v0</t>
+          <t>new_capacity vượt giới hạn an toàn - M2 Trang</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Chạy blackbox_fuzz() 300 lần</t>
+          <t>Kiểm tra SMT Z3 trên heap_alloc_bytes</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>v0: tìm được ít nhất 1 crash ZeroDivisionError (CWE-248/369); v1: hàm đã thay bằng kiểm tra 1 &lt;= rate &lt;= 24</t>
+          <t>Z3 chứng minh UNSAT: không tồn tại nghiệm vi phạm</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -798,28 +791,27 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>REQ-09, CON-02</t>
+          <t>REQ-07, CON-04</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Token ủy quyền thủ kho dài hơn 20 ký tự</t>
+          <t>H4: Rào chắn ngăn chặn tràn số cộng dồn</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>parse_auth_token (v0: buffer 20, Loi=buffer-overflow)</t>
+          <t>current_stock = 2.147.483.640, added_quantity = 20 - M3 Đô</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Sinh mã C
-Chạy check_c_source()</t>
+          <t>Gọi update_stock_quantity_v1</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>v0: dangerous-function (CWE-120); v1: 0 phát hiện</t>
+          <t>Phát hiện nguy cơ tràn số trước khi thực hiện, trả về ERR_OVERFLOW</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -836,28 +828,27 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>REQ-10</t>
+          <t>REQ-08, CON-04</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nhánh ẩn bỏ qua xác thực quyền thủ kho</t>
+          <t>H4: Từ chối số lượng nhập hàng âm</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Hàm Python manager_auth_bypass(admin_id, pin_code), magic_values = (31337, 8080)</t>
+          <t>added_quantity = -50 - M3 Đô</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Chạy black-box fuzz trước (kỳ vọng không tìm ra)
-Chạy concolic_fuzz()</t>
+          <t>Gọi update_stock_quantity_v1 với số âm</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Black-box: 0 lần chạm nhánh; concolic: tìm đúng (31337, 8080) sau vài lần thử (CWE-912)</t>
+          <t>Từ chối an toàn trả về ERR_NEGATIVE</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -874,33 +865,32 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>REQ-11, NFR-03</t>
+          <t>REQ-09, CON-04</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Rò rỉ bộ nhớ khi ghi nhật ký kiểm kê kho</t>
+          <t>H5: Rào chắn ngăn chặn tràn phép nhân đơn giá</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>write_audit_log (v0: Loi=memory-leak)</t>
+          <t>base_price lớn và rate lớn - M3 Đô</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Sinh mã C
-Chạy check_c_source()</t>
+          <t>Gọi scale_product_price_v1</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>v0: memory-leak (CWE-401); v1: 0 phát hiện</t>
+          <t>Kiểm tra base_price &gt; INT_MAX / rate, từ chối an toàn</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -912,34 +902,32 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>REQ-12</t>
+          <t>REQ-10, CON-05</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Chuỗi định dạng trong nhật ký kiểm kê</t>
+          <t>H6: Mutex đồng bộ hoàn toàn giữa 2 worker</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Mô hình con M5 — khuôn mẫu sinh mã của phần mềm không tạo được lỗi này</t>
+          <t>Cả 2 worker truy cập phiên kho - M2 Trang</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Nạp mô hình con M5 vào tab Ch1
-Chọn luồng M5-v0, kiểm tra AG(!format_string)
-Chọn luồng M5-v1, kiểm tra lại</t>
+          <t>Kiểm tra loại trừ lẫn nhau trên Kripke v1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>M5-v0: AG(!format_string) VI PHẠM (CWE-134); M5-v1: ĐÚNG</t>
+          <t>Thỏa mãn 100%, 0 vi phạm tranh chấp</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -951,28 +939,27 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>REQ-13, NFR-04</t>
+          <t>REQ-11, REQ-12</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Worker nhập kho và xuất kho cùng đóng phiên</t>
+          <t>H6: Con trỏ được gán NULL ngay sau free</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Cụm trạng thái h6_* trong mô hình kết hợp; LoaiTruLanNhau dòng 1 (nhap_locked, xuat_locked)</t>
+          <t>Gọi release_stock_items_v1 - M2 Trang</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Worker xuất kho tự động kích hoạt đúng lúc worker nhập kho đang giữ phiên
-Chạy check_mutual_exclusion(model, 'nhap_locked', 'xuat_locked')</t>
+          <t>Kiểm tra con trỏ sau khi free()</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>v0: Mutual exclusion VI PHẠM tại h6_tranh_chap (CWE-667); v1: ĐÚNG</t>
+          <t>list == NULL, triệt tiêu hoàn toàn lỗi Use-After-Free và Double-Free</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -989,108 +976,30 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>REQ-14, REQ-15</t>
+          <t>REQ-01 đến REQ-12</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Double free và use-after-free khi đóng phiên kho</t>
+          <t>Kiểm chứng toàn luồng quản lý kho an toàn v1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>close_inventory_session (double-free), release_item_buffer (use-after-free)</t>
+          <t>Mô hình kết hợp 27 trạng thái bản v1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Gộp mã C của 2 hàm
-Chạy check_c_source()</t>
+          <t>Chạy chay_kiem_chung_kripke.py</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>v0: double-free (CWE-415) và use-after-free (CWE-416); v1: 0 phát hiện</t>
+          <t>Không deadlock, 100% 18 công thức CTL THỎA MÃN</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TC-13</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>REQ-16, NFR-05, CON-07</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Mã PIN thủ kho còn trong bộ nhớ sau khi giải phóng</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Mô hình con M6</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Nạp mô hình con M6 vào tab Ch1
-Chọn luồng M6-v0, kiểm tra AG(!secret_residue)
-Chọn luồng M6-v1, kiểm tra lại</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>M6-v0: VI PHẠM (CWE-226/244, CWE-14); M6-v1 (explicit_bzero trước free): ĐÚNG</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>TC-14</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>REQ-17, REQ-18</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Toàn luồng quản lý phiếu kho</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Mô hình kết hợp (sheet MoHinhTrangThai)</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Chạy '1) Sinh Kripke + kiểm chứng (Ch1)'
-Kiểm tra deadlock, AF(flow_end), EF(stock_done), EF(input_rejected)</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Không deadlock; v0: AF(flow_end) và EF(input_rejected) VI PHẠM; v1: tất cả ĐÚNG</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1107,12 +1016,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="65" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -1146,7 +1055,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>H1: Hàm phân tích mã phiếu kho (parse_voucher_id) không được ghi vượt biên bộ đệm, kể cả khi mã dài ĐÚNG 16 ký tự (C1.2, C1.3)</t>
+          <t>H1: Hàm nạp chuỗi (ingest_raw_line) kiểm tra con trỏ, cap == 32 và từ chối chuỗi len &gt;= 32 (M1 Thọ)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -1168,7 +1077,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>H1: Mã phiếu kho hợp lệ không được bị cắt cụt hoặc biến đổi khi lưu vào bộ đệm (C1.4)</t>
+          <t>H1: Chuỗi mã phiếu hợp lệ (len &lt;= 31 byte) chép an toàn bằng memcpy và luôn gán '\0' tại cuối buffer (M1 Thọ)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -1190,7 +1099,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>H2: Kết quả cấp phát mảng kiện hàng (create_stock_items) phải được kiểm tra NULL trước khi sử dụng (C2.2)</t>
+          <t>H2: Hàm đọc token (get_token_field) từ chối con trỏ NULL và kiểm tra nghiêm ngặt 0 &lt;= field_idx &lt; token_count (M1 Thọ)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -1212,7 +1121,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>H2: Kích thước vùng nhớ cấp phát (số kiện x kích thước 1 kiện) không được tràn số hoặc âm (C2.3)</t>
+          <t>H2: Đảm bảo không đọc ngoài biên mảng token trong mọi kịch bản thực thi (M1 Thọ)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -1234,7 +1143,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>H2: Không được đọc trường dữ liệu của kiện hàng trước khi khởi tạo (C2.4)</t>
+          <t>H3: Sử dụng con trỏ tạm tmp khi gọi realloc; nếu OOM trả về STATUS_ERR_ALLOC và giữ nguyên vùng nhớ cũ (M2 Trang)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1244,7 +1153,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1165,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>H3: Tổng giá trị tồn kho không được tràn kiểu int32, kể cả khi cộng dồn nhiều dòng kiện hàng (C3.2, C3.3)</t>
+          <t>H3: Kiểm tra cận trên new_capacity &lt;= MAX_SAFE_CAPACITY trước khi tái cấp phát (M2 Trang)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>safety</t>
+          <t>memory</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1278,12 +1187,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>H3: Số lượng tồn kho, đơn giá, chiết khấu không được âm; tổng giá trị phiếu kho không được âm (C3.4)</t>
+          <t>H4: Cài đặt rào chắn defensive guard if (INT_MAX - stock &lt; added) return ERR_OVERFLOW (M3 Đô)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>safety</t>
+          <t>arithmetic</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1300,17 +1209,17 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>H3: Hàm tính tỷ lệ chiết khấu tồn kho không được gây lỗi không kiểm soát khi tỷ lệ/số kỳ = 0 (C3.5)</t>
+          <t>H4: Từ chối số lượng nhập hàng added_quantity &lt;= 0 trước khi cập nhật tồn kho (M3 Đô)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>functional</t>
+          <t>safety</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1231,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>H4: Hàm phân tích token ủy quyền thủ kho (parse_auth_token) không được tràn bộ đệm (C4.2)</t>
+          <t>H5: Kiểm tra tràn phép nhân if (INT_MAX / rate &lt; base_price) return ERR_OVERFLOW (M3 Đô)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>memory</t>
+          <t>arithmetic</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1344,12 +1253,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>H4: Mọi yêu cầu xuất nhập kho phải được xác thực chữ ký thủ kho; không được tồn tại nhánh ẩn bỏ qua kiểm tra (C4.3)</t>
+          <t>H6: Đồng bộ hóa phiên làm việc qua mutex ngăn chặn triệt để tranh chấp giữa 2 worker (M2 Trang)</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>safety</t>
+          <t>concurrency</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1366,7 +1275,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>H5: Bản ghi nhật ký kiểm kê kho (write_audit_log) phải được giải phóng trên mọi nhánh, kể cả nhánh lỗi (C5.2)</t>
+          <t>H6: Cơ chế phân quyền đảm bảo phiên làm việc chỉ được giải phóng đúng 1 lần (M2 Trang)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1376,7 +1285,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -1388,149 +1297,17 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>H5: Nội dung nhật ký kiểm kê có dữ liệu đầu vào không được dùng trực tiếp làm chuỗi định dạng của printf (C5.3)</t>
+          <t>H6: Gán list = NULL ngay lập tức sau lệnh free(list) triệt tiêu hoàn toàn dangling pointer (M2 Trang)</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>safety</t>
+          <t>memory</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>REQ-13</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>H6: Worker nhập kho và worker xuất kho tự động không được đồng thời giữ phiên quản lý kho (mutual exclusion) (C6.2)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>safety</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>REQ-14</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>H6: Phiên làm việc kho (close_inventory_session) chỉ được giải phóng đúng 1 lần (C6.3)</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>memory</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>REQ-15</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>H6: Không được truy cập phiên/bộ đệm kiện hàng (release_item_buffer) sau khi đã giải phóng (C6.4)</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>memory</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>REQ-16</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>H6: Mã PIN xác thực thủ kho phải được xóa trắng bằng lệnh không bị trình biên dịch loại bỏ trước khi giải phóng (C6.5)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>safety</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>REQ-17</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Toàn luồng: mọi đường xử lý quản lý kho cuối cùng phải kết thúc (thành công hoặc từ chối an toàn), không dừng ở trạng thái không an toàn</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>liveness</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>REQ-18</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Toàn luồng: luồng cập nhật kho thành công phải đạt tới được (mô hình không tầm thường) và đầu vào xấu phải có nhánh từ chối</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>liveness</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1355,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Hệ thống xử lý tối thiểu 300 giao dịch xuất nhập kho/giây trên phần cứng tham chiếu</t>
+          <t>Hệ thống xử lý an toàn tối thiểu 300 giao dịch nạp chuỗi và đọc token/giây</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -1595,7 +1372,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Phản hồi xác thực token ủy quyền thủ kho trong tối đa 2 giây (tránh timeout đồng bộ kho)</t>
+          <t>Rào chắn kiểm tra biên mảng phản hồi trong dưới 1 mili-giây</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -1612,7 +1389,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Bộ nhớ tiến trình quản lý kho không tăng quá 5% sau 1.000.000 lượt kiểm kê liên tiếp (chống rò rỉ bộ nhớ tích lũy)</t>
+          <t>Bộ nhớ tiến trình ổn định 100%, không rò rỉ (LeakSanitizer báo 0 byte leaked)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -1629,12 +1406,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Phiên làm việc kho tự hết hạn sau 15 phút nếu không có thao tác tiếp theo (worker timeout)</t>
+          <t>0 lỗi race condition được xác nhận bởi ThreadSanitizer</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1423,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Mã PIN xác thực và token thủ kho không được tồn tại trong bộ nhớ RAM quá thời gian hiệu lực phiên</t>
+          <t>Con trỏ mảng động sau free() được gán NULL ngay lập tức</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1663,12 +1440,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Nhật ký kiểm kê kho (audit log) được lưu trữ tối thiểu 24 tháng phục vụ thanh tra an toàn</t>
+          <t>Hiệu năng mở rộng mảng đạt O(1) trung bình</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1716,7 +1493,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Mã phiếu kho tối đa 16 ký tự ASCII (16 ký tự cần 17 byte kể cả '\0')</t>
+          <t>Chuỗi mã phiếu kho tối đa 31 ký tự ASCII (dung lượng định mức 32 byte kể cả '\0' - M1 Thọ)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -1733,7 +1510,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Mã token ủy quyền thủ kho tối đa 20 ký tự ASCII</t>
+          <t>Chỉ số đọc field_idx phải thỏa 0 &lt;= field_idx &lt; token_count (M1 Thọ)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -1750,7 +1527,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Mỗi phiếu có 1–100 dòng kiện hàng; số lượng mỗi dòng 1–1000; đơn giá 0–50.000.000 VND; giá trị mỗi dòng tối đa 50.000.000 VND</t>
+          <t>Danh mục hàng hóa mở rộng tối đa 10.000 phần tử (M2 Trang)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -1767,7 +1544,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Số tiền tính bằng VND; bản v0 dùng int 32-bit có dấu (tối đa 2.147.483.647); hạn mức 1 phiếu kho là 2.000.000.000 VND</t>
+          <t>Số lượng tồn kho và đơn giá nằm trong phạm vi signed int 32-bit dương (M3 Đô)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -1784,7 +1561,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Tỷ lệ phân bổ chiết khấu kho từ 1 đến 24 kỳ kiểm kê</t>
+          <t>Worker xuất kho tự động đồng bộ qua mutex (M2 Trang)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1801,27 +1578,10 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Chỉ dùng thư viện chuẩn C; phiên làm việc kho được bảo vệ bằng cơ chế khóa phiên an toàn</t>
+          <t>Mảng động cấp phát trên Heap bảo toàn quyền sở hữu khi OOM (M2 Trang)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CON-07</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Bộ đệm mã PIN xác thực 16 chữ số, chỉ tồn tại trong thời gian xử lý tác vụ kiểm kê</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1838,15 +1598,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="65" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1909,7 +1669,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Bắt đầu xử lý 1 phiếu kho hàng</t>
+          <t>Bắt đầu xử lý phiếu kho</t>
         </is>
       </c>
     </row>
@@ -1927,7 +1687,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>h1_ok, ket_thuc_tu_choi</t>
+          <t>h1_kiem_tra_bien</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -1937,91 +1697,91 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Nhận chuỗi mã phiếu kho từ giao diện</t>
+          <t>Nhận chuỗi mã phiếu kho vào bộ đệm stack (M1 Thọ)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>h1_ok</t>
+          <t>h1_kiem_tra_bien</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>h1, input_ok</t>
+          <t>h1, checking_bounds</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>h2_vao</t>
+          <t>h1_ok, h1_tu_choi</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>C1.1</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Mã phiếu chép đủ, có '\0' (an toàn)</t>
+          <t>Kiểm tra độ dài len &lt; 32</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>h1_tran_1_byte</t>
+          <t>h1_ok</t>
         </is>
       </c>
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>h1, buffer_overflow, off_by_one, violation</t>
+          <t>h1, copy_safe, input_ok</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>dung_khong_an_toan</t>
+          <t>h2_vao</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>C1.2</t>
+          <t>C1.1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Mã ĐÚNG 16 ký tự: strcpy ghi 17 byte, '\0' đè sang biến kề (lỗi ẩn)</t>
+          <t>Sao chép an toàn bằng memcpy và gán NUL</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>h1_tran_bo_dem</t>
+          <t>h1_tu_choi</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>h1, buffer_overflow, violation</t>
+          <t>h1, input_rejected</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>dung_khong_an_toan</t>
+          <t>ket_thuc_tu_choi</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>C1.3</t>
+          <t>C1.2</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Mã &gt; 16 ký tự: tràn bộ đệm stack</t>
+          <t>Từ chối chuỗi len &gt;= 32 trước khi sao chép</t>
         </is>
       </c>
     </row>
@@ -2034,12 +1794,12 @@
       <c r="B7" s="2" t="n"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>h2, allocating</t>
+          <t>h2, indexing</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>h2_ok, ket_thuc_tu_choi</t>
+          <t>h2_kiem_tra_chi_so</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -2049,137 +1809,137 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>items = malloc(n * sizeof(Item))</t>
+          <t>Nhận chỉ số đọc trường token (M1 Thọ)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>h2_ok</t>
+          <t>h2_kiem_tra_chi_so</t>
         </is>
       </c>
       <c r="B8" s="2" t="n"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>h2, allocated, initialized</t>
+          <t>h2, checking_index</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>h3_vao</t>
+          <t>h2_ok, h2_tu_choi</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>C2.1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Cấp phát thành công và đã khởi tạo (an toàn)</t>
+          <t>Kiểm tra 0 &lt;= field_idx &lt; token_count</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>h2_null</t>
+          <t>h2_ok</t>
         </is>
       </c>
       <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>h2, null_deref, violation</t>
+          <t>h2, read_safe, index_ok</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>dung_khong_an_toan</t>
+          <t>h3_vao</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>C2.2</t>
+          <t>C2.1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>malloc trả NULL nhưng vẫn ghi vào (lỗi ẩn: chỉ khi cạn bộ nhớ)</t>
+          <t>Đọc token thành công trong phạm vi mảng</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>h2_sai_kich_thuoc</t>
+          <t>h2_tu_choi</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>h2, alloc_size_overflow, heap_overflow, violation</t>
+          <t>h2, index_rejected</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>dung_khong_an_toan</t>
+          <t>ket_thuc_tu_choi</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>C2.3</t>
+          <t>C2.2</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>n*48 tràn int32 hoặc n âm: cấp phát sai kích thước rồi ghi tràn heap (lỗi ẩn)</t>
+          <t>Từ chối chỉ số ngoài biên hoặc mảng NULL</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>h2_doc_rac</t>
+          <t>h3_vao</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>h2, uninit_read, violation</t>
+          <t>h3, allocating</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>dung_khong_an_toan</t>
+          <t>h3_kiem_tra_heap</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>C2.4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Đọc status kiện hàng khi chưa khởi tạo (lỗi ẩn)</t>
+          <t>Mở rộng mảng động danh mục hàng (M2 Trang)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>h3_vao</t>
+          <t>h3_kiem_tra_heap</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>h3, computing</t>
+          <t>h3, realloc_temp</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>h3_ok, ket_thuc_tu_choi</t>
+          <t>h3_ok, h3_tu_choi</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2189,7 +1949,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Tính tổng tồn kho = Σ đơn giá × SL + phí đóng gói − chiết khấu</t>
+          <t>Dùng con trỏ tạm tmp kiểm tra kết quả realloc</t>
         </is>
       </c>
     </row>
@@ -2202,7 +1962,7 @@
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>h3, amount_ok</t>
+          <t>h3, realloc_ok, owner_valid</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -2217,389 +1977,389 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Tổng giá trị tồn kho nằm trong miền hợp lệ (an toàn)</t>
+          <t>Mở rộng thành công, cập nhật con trỏ chính</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>h3_tran_so</t>
+          <t>h3_tu_choi</t>
         </is>
       </c>
       <c r="B14" s="2" t="n"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>h3, int_overflow, violation</t>
+          <t>h3, owner_preserved</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>dung_khong_an_toan</t>
+          <t>ket_thuc_tu_choi</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>C3.2/C3.3</t>
+          <t>C3.2</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Tràn int32 khi nhân đơn giá x SL hoặc khi cộng dồn nhiều kiện (lỗi ẩn)</t>
+          <t>OOM: bảo toàn mảng cũ, từ chối an toàn</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>h3_so_am</t>
+          <t>h4_vao</t>
         </is>
       </c>
       <c r="B15" s="2" t="n"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>h3, negative_amount, violation</t>
+          <t>h4, computing</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>dung_khong_an_toan</t>
+          <t>h4_kiem_tra_rao_chan</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>C3.4</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>SL/chiết khấu âm hoặc chiết khấu &gt; tạm tính: tổng âm (lỗi ẩn)</t>
+          <t>Cộng dồn tồn kho mới (M3 Đô)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>h3_chia_0</t>
+          <t>h4_kiem_tra_rao_chan</t>
         </is>
       </c>
       <c r="B16" s="2" t="n"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>h3, div_by_zero, violation</t>
+          <t>h4, guard_checking</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>dung_khong_an_toan</t>
+          <t>h4_ok, h4_tu_choi</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>C3.5</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Phân bổ chiết khấu với kỳ hạn = 0: chia cho 0</t>
+          <t>Kiểm tra added &gt; 0 và added &lt;= INT_MAX - stock</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>h4_vao</t>
+          <t>h4_ok</t>
         </is>
       </c>
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>h4, token_received</t>
+          <t>h4, sum_safe</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>h4_ok, h4_tu_choi_quyen</t>
+          <t>h5_vao</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>C4.1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Nhận token ủy quyền từ thủ kho</t>
+          <t>Cộng dồn tồn kho an toàn</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>h4_ok</t>
+          <t>h4_tu_choi</t>
         </is>
       </c>
       <c r="B18" s="2" t="n"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>h4, token_verified</t>
+          <t>h4, overflow_prevented, negative_rejected</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>h5_vao</t>
+          <t>ket_thuc_tu_choi</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>C4.1</t>
+          <t>C4.2</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Token hợp lệ, chữ ký đúng quyền thủ kho (an toàn)</t>
+          <t>Từ chối số âm hoặc nguy cơ tràn số</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>h4_tu_choi_quyen</t>
+          <t>h5_vao</t>
         </is>
       </c>
       <c r="B19" s="2" t="n"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>h4, token_rejected</t>
+          <t>h5, scaling</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>h6_phien_ranh</t>
+          <t>h5_kiem_tra_nhan</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>C4.1</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Token sai quyền bị từ chối (an toàn) — phiên do worker timeout đóng</t>
+          <t>Quy đổi đơn giá theo tỉ giá (M3 Đô)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>h4_tran_token</t>
+          <t>h5_kiem_tra_nhan</t>
         </is>
       </c>
       <c r="B20" s="2" t="n"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>h4, buffer_overflow, violation</t>
+          <t>h5, mul_guard_checking</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>dung_khong_an_toan</t>
+          <t>h5_ok, h5_tu_choi</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>C4.2</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Token &gt; 20 ký tự: tràn bộ đệm</t>
+          <t>Kiểm tra base_price &lt;= INT_MAX / rate</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>h4_nhanh_an</t>
+          <t>h5_ok</t>
         </is>
       </c>
       <c r="B21" s="2" t="n"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>h4, hidden_bypass, violation</t>
+          <t>h5, scale_safe</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>dung_khong_an_toan</t>
+          <t>h6_phien_ranh</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>C4.3</t>
+          <t>C5.1</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Nhánh ẩn bỏ qua kiểm tra quyền thủ kho (31337, 8080) (lỗi ẩn)</t>
+          <t>Nhân tỉ giá an toàn</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>h5_vao</t>
+          <t>h5_tu_choi</t>
         </is>
       </c>
       <c r="B22" s="2" t="n"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>h5, logging</t>
+          <t>h5, mul_overflow_prevented</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>h5_ok</t>
+          <t>ket_thuc_tu_choi</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>C5.2</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>e = malloc(LogEntry); ghi nhật ký kiểm kê kho</t>
+          <t>Từ chối tỉ giá gây tràn số</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>h5_ok</t>
+          <t>h6_phien_ranh</t>
         </is>
       </c>
       <c r="B23" s="2" t="n"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>h5, log_freed</t>
+          <t>h6, sess_free</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>h6_phien_ranh</t>
+          <t>h6_nhap_giu, h6_xuat_giu</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>C5.1</t>
+          <t>H6</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Ghi log kiểm kê xong và free(e) (an toàn)</t>
+          <t>Phiên kho rảnh (M2 Trang)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>h5_ro_ri</t>
+          <t>h6_nhap_giu</t>
         </is>
       </c>
       <c r="B24" s="2" t="n"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>h5, mem_leak, violation</t>
+          <t>h6, nhap_locked</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>dung_khong_an_toan</t>
+          <t>h6_giai_phong</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>C5.2</t>
+          <t>C6.1</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Nhánh lỗi return sớm, quên free (lỗi ẩn: rò rỉ tích lũy)</t>
+          <t>Worker nhập kho giữ khóa mutex an toàn</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>h5_format_string</t>
+          <t>h6_xuat_giu</t>
         </is>
       </c>
       <c r="B25" s="2" t="n"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>h5, format_string, violation</t>
+          <t>h6, xuat_locked</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>dung_khong_an_toan</t>
+          <t>h6_giai_phong</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>C5.3</t>
+          <t>C6.1</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>printf(msg) với msg chứa định dạng %x/%n (lỗi ẩn)</t>
+          <t>Worker xuất kho tự động giữ khóa mutex</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>h6_phien_ranh</t>
+          <t>h6_giai_phong</t>
         </is>
       </c>
       <c r="B26" s="2" t="n"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>h6, sess_free</t>
+          <t>h6, pointer_nullified, zero_leak</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>h6_nhap_giu, h6_xuat_giu</t>
+          <t>ket_thuc_ok</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>H6</t>
+          <t>C6.1</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Phiên kho đang mở, chưa worker nào giữ</t>
+          <t>Giải phóng tài nguyên và gán list = NULL</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>h6_nhap_giu</t>
+          <t>ket_thuc_ok</t>
         </is>
       </c>
       <c r="B27" s="2" t="n"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>h6, nhap_locked</t>
+          <t>flow_end, stock_done, mem_clean, safe</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>h6_giai_phong</t>
+          <t>ket_thuc_ok</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -2609,259 +2369,35 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Worker nhập kho đang giữ phiên</t>
+          <t>Hoàn tất phiên an toàn</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>h6_xuat_giu</t>
+          <t>ket_thuc_tu_choi</t>
         </is>
       </c>
       <c r="B28" s="2" t="n"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>h6, xuat_locked</t>
+          <t>flow_end, input_rejected, mem_clean, safe</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>h6_giai_phong</t>
+          <t>ket_thuc_tu_choi</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>C6.1</t>
+          <t>C1.2</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Worker xuất kho tự động (15 phút) đang giữ phiên</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>h6_tranh_chap</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n"/>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>h6, nhap_locked, xuat_locked, race, violation</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>h6_double_free, h6_uaf</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>C6.2</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Cả 2 worker cùng giữ phiên (race condition, lỗi ẩn)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>h6_double_free</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n"/>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>h6, double_free, violation</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>dung_khong_an_toan</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>C6.3</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Cả 2 worker cùng free(session) (lỗi ẩn)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>h6_uaf</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n"/>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>h6, use_after_free, violation</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>dung_khong_an_toan</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>C6.4</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Worker đến sau ghi vào phiên kho đã free (lỗi ẩn)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>h6_giai_phong</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n"/>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>h6, releasing</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>ket_thuc_ok</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>C6.1</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Giải phóng bộ đệm mã PIN và phiên làm việc</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>h6_con_ma_pin</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n"/>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>h6, secret_residue, violation</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>dung_khong_an_toan</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>C6.5</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Mã PIN thủ kho còn trong heap sau free (memset bị -O2 loại bỏ) (lỗi ẩn)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>ket_thuc_ok</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n"/>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>flow_end, stock_done, mem_clean</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>ket_thuc_ok</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Kết thúc: đã xử lý phiếu kho, bộ nhớ sạch</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>ket_thuc_tu_choi</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="n"/>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>flow_end, input_rejected, mem_clean</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>ket_thuc_tu_choi</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Kết thúc: từ chối đầu vào xấu một cách an toàn</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>dung_khong_an_toan</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n"/>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>unsafe_halt</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>dung_khong_an_toan</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Trạng thái hút sau vi phạm (error location trong BMC)</t>
+          <t>Từ chối an toàn có kiểm soát</t>
         </is>
       </c>
     </row>
@@ -2876,10 +2412,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="65" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -2903,19 +2439,19 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Safety tổng: không bao giờ đạt trạng thái vi phạm nào</t>
+          <t>Safety tổng: không bao giờ đạt trạng thái vi phạm nào (v1 THỎA MÃN)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>AG(!buffer_overflow)</t>
+          <t>AG(!stack_buffer_overflow)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Safety C1.2, C1.3, C4.2 — CWE-120/787</t>
+          <t>Safety H1: không có vết tràn stack (v1 THỎA MÃN)</t>
         </is>
       </c>
     </row>
@@ -2927,223 +2463,187 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Safety C1.2 — CWE-193 (lỗi ẩn: mã đúng 16 ký tự)</t>
+          <t>Safety H1: không có lỗi ghi đè null terminator (v1 THỎA MÃN)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>AG(!null_deref)</t>
+          <t>AG(!out_of_bounds_read)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Safety C2.2 — CWE-476/690</t>
+          <t>Safety H2: không có lỗi đọc ngoài biên token (v1 THỎA MÃN)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>AG(!heap_overflow)</t>
+          <t>AG(!null_deref)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Safety C2.3 — CWE-680/122</t>
+          <t>Safety H2: không dereference con trỏ NULL (v1 THỎA MÃN)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>AG(!uninit_read)</t>
+          <t>AG(!alloc_size_overflow)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Safety C2.4 — CWE-457/908</t>
+          <t>Safety H3: không tràn kích thước cấp phát Heap (v1 THỎA MÃN)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>AG(!int_overflow)</t>
+          <t>AG(!mem_leak)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Safety C3.2, C3.3 — CWE-190</t>
+          <t>Safety H3: không rò rỉ bộ nhớ khi OOM (v1 THỎA MÃN)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>AG(!negative_amount)</t>
+          <t>AG(!int_overflow)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Safety C3.4 — CWE-191/839</t>
+          <t>Safety H4, H5: không tràn số nguyên (v1 THỎA MÃN)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AG(!div_by_zero)</t>
+          <t>AG(!negative_amount)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Safety C3.5 — CWE-369</t>
+          <t>Safety H4: từ chối số lượng nhập âm (v1 THỎA MÃN)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AG(!hidden_bypass)</t>
+          <t>AG(!race)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Safety C4.3 — CWE-912/CWE-807</t>
+          <t>Safety H6: mutex đồng bộ hoàn toàn (v1 THỎA MÃN)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>AG(!mem_leak)</t>
+          <t>AG(!double_free)</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Safety C5.2 — CWE-401</t>
+          <t>Safety H6: không giải phóng đúp (v1 THỎA MÃN)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>AG(!format_string)</t>
+          <t>AG(!use_after_free)</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Safety C5.3 — CWE-134</t>
+          <t>Safety H6: gán NULL sau free triệt tiêu UAF (v1 THỎA MÃN)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>AG(!race)</t>
+          <t>AF(flow_end)</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Safety C6.2 — CWE-362/667</t>
+          <t>Liveness: mọi luồng đều kết thúc có kiểm soát (v1 THỎA MÃN)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>AG(!double_free)</t>
+          <t>EF(stock_done)</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Safety C6.3 — CWE-415</t>
+          <t>Khả đạt: tồn tại đường đi hoàn tất phiên an toàn (v1 THỎA MÃN)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>AG(!use_after_free)</t>
+          <t>EF(input_rejected)</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Safety C6.4 — CWE-416</t>
+          <t>Khả đạt: tồn tại nhánh từ chối an toàn có kiểm soát (v1 THỎA MÃN)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>AG(!secret_residue)</t>
+          <t>EG(!violation)</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Safety C6.5 — CWE-226/CWE-14</t>
+          <t>Tồn tại đường đi an toàn xuyên suốt chu trình (v1 THỎA MÃN)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>AF(flow_end)</t>
+          <t>EF(nhap_locked)</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Liveness REQ-17: mọi lượt xử lý đều kết thúc hợp lệ</t>
+          <t>Cụm khóa phiên nhập kho hoạt động được</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>EF(stock_done)</t>
+          <t>EF(xuat_locked)</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Khả đạt REQ-18: tồn tại đường đi cập nhật kho thành công</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>EF(input_rejected)</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Khả đạt REQ-18: tồn tại nhánh từ chối đầu vào xấu (v0 KHÔNG có -&gt; VI PHẠM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>EG(!violation)</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Tồn tại ít nhất 1 đường đi luôn an toàn</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>EF(nhap_locked)</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Khả đạt của cụm khóa phiên (mô hình khóa không tầm thường)</t>
+          <t>Cụm khóa phiên xuất kho tự động hoạt động được</t>
         </is>
       </c>
     </row>
@@ -3158,10 +2658,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -3220,18 +2720,6 @@
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>mem_clean</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>use_after_free</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>mem_clean</t>
         </is>
@@ -3251,15 +2739,15 @@
   <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="49" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3312,7 +2800,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>parse_voucher_id</t>
+          <t>ingest_raw_line</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -3327,25 +2815,25 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>raw_voucher_id</t>
+          <t>dst, cap, raw_line</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>H1 — buffer 17 byte cho mã 16 ký tự (sửa C1.2)</t>
+          <t>H1 — Nạp chuỗi an toàn phòng thủ (M1 Thọ)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>parse_auth_token</t>
+          <t>get_token_field</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -3355,30 +2843,28 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>buffer_copy</t>
+          <t>array_read</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>raw_token</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>21</v>
-      </c>
+          <t>token_offsets, token_count, field_idx</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>H4 — buffer 21 byte cho token 20 ký tự</t>
+          <t>H2 — Đọc token an toàn phòng thủ (M1 Thọ)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>create_stock_items</t>
+          <t>expand_stock_items</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -3391,23 +2877,27 @@
           <t>alloc_release</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>list, new_capacity</t>
+        </is>
+      </c>
       <c r="E4" s="2" t="n">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>H2 — calloc + kiểm tra NULL + n trong 1..100</t>
+          <t>H3 — realloc an toàn bảo toàn vùng nhớ qua tmp (M2 Trang)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>write_audit_log</t>
+          <t>release_stock_items</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -3420,23 +2910,27 @@
           <t>alloc_release</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n"/>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
       <c r="E5" s="2" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="2" t="n"/>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>H5 — goto cleanup: free trên mọi nhánh</t>
+          <t>H6 — free() và gán con trỏ = NULL (M2 Trang)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>close_inventory_session</t>
+          <t>update_stock_quantity</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -3446,26 +2940,28 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>alloc_release</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n">
-        <v>4</v>
-      </c>
+          <t>arithmetic</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>current_stock, added_quantity</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="n"/>
       <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>H6 — free 1 lần, gán NULL, trạng thái CLOSED</t>
+          <t>H4 — Cộng tồn kho an toàn phòng thủ (M3 Đô)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>release_item_buffer</t>
+          <t>scale_product_price</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -3475,41 +2971,43 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>alloc_release</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n">
-        <v>16</v>
-      </c>
+          <t>arithmetic</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>base_price, rate</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="n"/>
       <c r="H7" s="2" t="n"/>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>H6 — explicit_bzero rồi free, không dùng lại</t>
+          <t>H5 — Nhân tỉ giá an toàn phòng thủ (M3 Đô)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>add_packing_fee</t>
+          <t>calc_batch_capacity</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>python</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>arithmetic</t>
+          <t>divide</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>subtotal, packing_fee</t>
+          <t>total_items, batch_size</t>
         </is>
       </c>
       <c r="E8" s="2" t="n"/>
@@ -3518,7 +3016,7 @@
       <c r="H8" s="2" t="n"/>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>H3 — trích AST cho Chương 3</t>
+          <t>H3 — Kiểm tra batch_size &gt; 0 trước khi chia</t>
         </is>
       </c>
     </row>
@@ -3533,13 +3031,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
     <col width="65" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
     <col width="65" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -3573,135 +3071,108 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>stock_total_int32</t>
+          <t>stock_addition_overflow</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>subtotal, packing_fee</t>
+          <t>current_stock, added_quantity</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>subtotal &gt;= 0 and subtotal &lt;= 2000000000 and packing_fee &gt;= 0 and packing_fee &lt;= 500000 and subtotal + packing_fee &gt; 2147483647</t>
+          <t>current_stock &gt;= 0 and added_quantity &gt;= 1 and current_stock + added_quantity &gt; 2147483647</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>subtotal + packing_fee</t>
+          <t>current_stock + added_quantity</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>v1: hạn mức phiếu kho 2 tỷ -&gt; UNSAT</t>
+          <t>H4 — rào chắn ngăn chặn hoàn toàn (Z3 UNSAT trên v1 - M3 Đô)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>line_amount_mul</t>
+          <t>heap_alloc_bytes</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>price, qty</t>
+          <t>new_capacity, item_size</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>price &gt;= 0 and price &lt;= 50000000 and qty &gt;= 1 and qty &lt;= 1000 and price * qty &lt;= 50000000 and price * qty &gt; 2147483647</t>
+          <t>new_capacity &gt;= 1 and item_size == 48 and new_capacity * item_size &gt; 2147483647</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>price * qty</t>
+          <t>new_capacity * item_size</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>v1: nhân bằng int64 rồi kiểm tra hạn mức dòng trước khi lưu -&gt; UNSAT</t>
+          <t>H3 — rào chắn giới hạn MAX_SAFE_CAPACITY (Z3 UNSAT - M2 Trang)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>accumulated_total</t>
+          <t>price_multiplication_overflow</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>total_before, line_total</t>
+          <t>base_price, rate</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>total_before &gt;= 0 and line_total &gt;= 0 and line_total &lt;= 50000000 and total_before &lt;= 2000000000 - line_total and total_before + line_total &gt; 2147483647</t>
+          <t>base_price &gt; 0 and rate &gt; 1 and base_price * rate &gt; 2147483647</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>total_before + line_total</t>
+          <t>base_price * rate</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>v1: kiểm tra hạn mức TRƯỚC mỗi lần cộng (bước quy nạp) -&gt; UNSAT</t>
+          <t>H5 — rào chắn kiểm tra trần nhân (Z3 UNSAT - M3 Đô)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>alloc_bytes</t>
+          <t>negative_quantity_check</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>n_items, item_size</t>
+          <t>added_quantity</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>n_items &gt;= 1 and n_items &lt;= 100 and item_size == 48 and n_items * item_size &gt; 2147483647</t>
+          <t>added_quantity &lt; 0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>n_items * item_size</t>
+          <t>added_quantity</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>v1: n trong 1..100 -&gt; UNSAT</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>negative_total</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>subtotal, discount</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>subtotal &gt;= 0 and subtotal &lt;= 2000000000 and discount &gt;= 0 and discount &lt;= subtotal and subtotal - discount &lt; 0</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>subtotal - discount</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>v1: 0 &lt;= chiết khấu &lt;= tạm tính -&gt; UNSAT</t>
+          <t>H4 — từ chối số âm trước khi xử lý (Z3 UNSAT - M3 Đô)</t>
         </is>
       </c>
     </row>

--- a/01_spec/quanly_khohang_v1.xlsx
+++ b/01_spec/quanly_khohang_v1.xlsx
@@ -512,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -562,444 +562,1060 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TC-01</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>REQ-01, CON-01</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>H1: Nạp chuỗi 32 và 33 byte bị từ chối an toàn</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>ingest_raw_line_v1 có rào chắn kiểm tra len &lt; 32 - M1 Thọ</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Gọi ingest_raw_line_v1 với chuỗi dài 32 và 33 ký tự</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Hàm từ chối xử lý, trả về mã lỗi an toàn -2, 0 byte bị ghi đè</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TC-M1-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>REQ-1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Nạp dòng chuỗi chuẩn độ dài ngắn (len = 15 &lt; 32 bytes) vào buffer</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Chuỗi raw_line hợp lệ: SP001;GaoST25;100;25000 (23 bytes)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Khởi tạo buffer stack 32 byte
+Thực hiện nạp chuỗi raw_line vào buffer</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>v0 và v1 đều nạp chuỗi thành công, buffer nhận đúng nội dung</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TC-02</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>REQ-02, CON-01</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>H1: Nạp chuỗi hợp lệ 31 byte thành công</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>char buffer[32], cap = 32, chuỗi dài 31 ký tự - M1 Thọ</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Gọi ingest_raw_line_v1 với chuỗi 31 byte</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Trả về 31, sao chép thành công và kết thúc bằng '\0'</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TC-M1-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>REQ-1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Nạp dòng chuỗi cận trên an toàn (len = 31 bytes có null-terminator)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Chuỗi raw_line dài chính xác 31 ký tự + 1 byte null = 32 byte</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Khởi tạo buffer stack 32 byte
+Nạp chuỗi biên 31 byte vào buffer</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>v0 và v1 đều sao chép an toàn, ký tự kết thúc chuỗi '\0' được bảo toàn</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TC-03</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>REQ-03, CON-02</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>H2: Đọc token ngoài biên bị từ chối có kiểm soát</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>token_count = 4, field_idx = 4 hoặc field_idx = -1 - M1 Thọ</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Gọi get_token_field_v1 với chỉ số ngoài biên</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Rào chắn phát hiện chỉ số vi phạm, từ chối an toàn trả về -2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TC-M1-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>REQ-2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Đọc trường token đầu tiên (field_idx = 0) từ danh sách token hợp lệ</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Mảng token đã phân tách gồm 4 trường SP001, GaoST25, 100, 25000 (token_count = 4)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Gọi hàm get_token_field với field_idx = 0
+Lấy giá trị mã hàng</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Truy xuất thành công trường mã hàng SP001, không lỗi</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TC-04</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>REQ-04, CON-02</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>H2: Đọc token với con trỏ mảng NULL</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>token_offsets = NULL - M1 Thọ</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Gọi get_token_field_v1 với con trỏ NULL</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Rào chắn phát hiện mảng NULL, trả về -1</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TC-M1-04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>REQ-2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Đọc trường token cuối cùng (field_idx = token_count - 1)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>token_count = 4, truy xuất trường đơn giá tại chỉ số 3</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Gọi hàm get_token_field với field_idx = 3
+Lấy giá trị đơn giá</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Truy xuất thành công trường đơn giá 25000</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TC-05</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>REQ-05, CON-03</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>H3: OOM khi realloc bảo toàn vùng nhớ cũ</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>mock_realloc trả về NULL - M2 Trang</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Gọi expand_stock_items_v1 khi hết RAM</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Bảo toàn 100% con trỏ cũ qua biến tạm tmp, trả về STATUS_ERR_ALLOC</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TC-M1-05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>REQ-3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Kiểm toán an toàn chu trình I/O toàn diện không vi phạm bộ nhớ</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Chạy qua toàn bộ chu trình nạp chuỗi và đọc token</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Kiểm tra bất biến AG(!violation) trên toàn bộ không gian trạng thái</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>v0: Vi phạm an toàn (CWE-120/125); v1: Thỏa mãn 100% AG(!violation)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TC-06</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>REQ-06, CON-03</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>H3: Kích thước mở rộng được chặn cận trên</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>new_capacity vượt giới hạn an toàn - M2 Trang</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Kiểm tra SMT Z3 trên heap_alloc_bytes</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Z3 chứng minh UNSAT: không tồn tại nghiệm vi phạm</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TC-M1-06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>REQ-4</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Kích hoạt lỗi tràn bộ đệm stack với chuỗi dữ liệu vượt ngưỡng (len = 64 bytes)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Chuỗi raw_line chứa 64 ký tự (vượt quá stack buffer 32 byte)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Gọi ingest_raw_line với chuỗi 64 byte
+Quan sát vùng nhớ stack liền kề</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>v0: Ghi đè frame stack và con trỏ trả về (CWE-120/121); v1: Chặn từ chối an toàn do len &gt;= 32</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TC-07</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>REQ-07, CON-04</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>H4: Rào chắn ngăn chặn tràn số cộng dồn</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>current_stock = 2.147.483.640, added_quantity = 20 - M3 Đô</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Gọi update_stock_quantity_v1</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Phát hiện nguy cơ tràn số trước khi thực hiện, trả về ERR_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TC-M1-07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>REQ-4</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Bắt lỗi Off-by-one khi chuỗi có đúng 32 byte dữ liệu thiếu null-terminator</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Chuỗi đầu vào có đúng 32 ký tự, không còn chỗ cho ký tự null kết thúc chuỗi</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sao chép 32 byte vào buffer[32] bằng strcpy
+Đọc chuỗi sau khi sao chép</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>v0: Đọc tràn qua biến tiếp theo trên stack do thiếu null (CWE-193); v1: buffer[31] = '\0'</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TC-08</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>REQ-08, CON-04</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>H4: Từ chối số lượng nhập hàng âm</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>added_quantity = -50 - M3 Đô</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Gọi update_stock_quantity_v1 với số âm</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Từ chối an toàn trả về ERR_NEGATIVE</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TC-M1-08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>REQ-4</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Phát hiện lỗi Stack Buffer Overflow bằng AddressSanitizer (ASan Crash Trigger)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Biên dịch mã nguồn C với flag -fsanitize=address</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Thực thi hàm ingest_raw_line với chuỗi 48 ký tự
+Ghi nhận cảnh báo từ ASan</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>v0: ASan báo lỗi ERROR: AddressSanitizer: stack-buffer-overflow; v1: 0 crash</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TC-09</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>REQ-09, CON-04</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>H5: Rào chắn ngăn chặn tràn phép nhân đơn giá</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>base_price lớn và rate lớn - M3 Đô</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Gọi scale_product_price_v1</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Kiểm tra base_price &gt; INT_MAX / rate, từ chối an toàn</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TC-M1-09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>REQ-5</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Bắt lỗi đọc ngoài biên mảng token khi chỉ số vượt trần (field_idx &gt;= token_count)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>token_count = 4, yêu cầu đọc trường tại field_idx = 4 hoặc field_idx = 10</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Gọi get_token_field(4, 4)
+Kiểm tra con trỏ token trả về</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>v0: Đọc ngoài biên mảng con trỏ token (CWE-125); v1: Phát hiện và trả về NULL/mã lỗi an toàn</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>TC-10</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>REQ-10, CON-05</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>H6: Mutex đồng bộ hoàn toàn giữa 2 worker</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Cả 2 worker truy cập phiên kho - M2 Trang</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Kiểm tra loại trừ lẫn nhau trên Kripke v1</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Thỏa mãn 100%, 0 vi phạm tranh chấp</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TC-M1-10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>REQ-5</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Bắt lỗi đọc ngoài biên mảng token khi chỉ số âm (field_idx = -1 &lt; 0)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Yêu cầu đọc trường với chỉ số âm field_idx = -1</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Gọi get_token_field(4, -1)
+Kiểm tra phản hồi của hệ thống</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>v0: Đọc vùng nhớ phía trước mảng token (CWE-125); v1: Chặn ngay tại điều kiện field_idx &lt; 0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TC-11</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>REQ-11, REQ-12</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>H6: Con trỏ được gán NULL ngay sau free</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Gọi release_stock_items_v1 - M2 Trang</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Kiểm tra con trỏ sau khi free()</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>list == NULL, triệt tiêu hoàn toàn lỗi Use-After-Free và Double-Free</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TC-M1-11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>REQ-6</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Kiểm tra tính sống: Không xảy ra deadlock trong toàn bộ chu trình xử lý I/O</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Mô hình chuyển trạng thái Kripke của module M1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Duyệt qua tất cả 7 trạng thái
+Kiểm tra bậc ra out-degree của từng trạng thái</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mọi trạng thái đều có out-degree &gt;= 1, 0 deadlock, công thức AF(done) thỏa mãn trên v1</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>TC-12</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>REQ-01 đến REQ-12</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Kiểm chứng toàn luồng quản lý kho an toàn v1</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Mô hình kết hợp 27 trạng thái bản v1</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Chạy chay_kiem_chung_kripke.py</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Không deadlock, 100% 18 công thức CTL THỎA MÃN</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TC-M1-12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>REQ-1, REQ-2, REQ-3, REQ-4, REQ-5, REQ-6</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Kiểm thử hồi quy đối chứng toàn diện pytest (Regression Verification Suite)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Bộ test pytest tự động test_verify_v0_cases_on_v1.py</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Chạy kiểm thử toàn bộ test cases trên bản v0
+Chạy kiểm thử toàn bộ test cases trên bản v1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>v0: Bắt đầy đủ lỗi CWE-120/121, CWE-193, CWE-125; v1: 100% PASSED</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TC-M2-01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>REQ-1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Khởi tạo mảng động danh mục hàng ban đầu (Initial Capacity)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Khởi tạo danh sách rỗng product_list_init(&amp;list)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Gọi hàm khởi tạo danh mục
+Kiểm tra count == 0, capacity == 16, con trỏ items != NULL</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Thành công: Cấp phát đúng 16 ô nhớ ban đầu trên Heap</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TC-M2-02</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>REQ-1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Thêm sản phẩm tới chạm ngưỡng dung lượng chưa mở rộng (Fill to Capacity)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Danh sách đang có capacity = 16</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Thêm liên tiếp 16 sản phẩm hợp lệ vào danh sách
+Kiểm tra count == 16, capacity == 16</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Thành công: 16 sản phẩm được lưu trọn vẹn, chưa kích hoạt realloc</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TC-M2-03</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>REQ-1, REQ-6</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Tự động nhân đôi dung lượng khi thêm sản phẩm thứ 17 (Capacity Doubling)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Danh sách đã đầy 16 phần tử, thêm phần tử thứ 17</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Gọi add_product thêm sản phẩm thứ 17
+Kiểm tra capacity tăng từ 16 lên 32, count == 17</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Thành công: Thuật toán nhân đôi mảng động cấp phát vùng nhớ mới an toàn</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TC-M2-04</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>REQ-6</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Kiểm tra tràn số nguyên khi tính toán kích thước mở rộng (Integer Overflow in Capacity)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>current_capacity vượt ngưỡng an toàn (ví dụ: SIZE_MAX / 2)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Chạy kiểm tra SMT Z3 trên điều kiện heap_alloc_bytes
+Thực thi hàm calc_expand_capacity_v0 với factor lớn</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>v0: Phép nhân tràn số âm/nhỏ gây cấp phát thiếu ô nhớ; v1: Rào chắn từ chối mở rộng</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TC-M2-05</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>REQ-4</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Mô phỏng sự cố OOM khi realloc mảng động (Fault Injection OOM NULL)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Hệ thống cạn kiệt RAM, mock_realloc trả về NULL</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Ép hàm realloc trả về NULL khi mảng đầy cần mở rộng
+Quan sát phản ứng của hàm mở rộng</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>v0: Gán list = NULL làm mất sạch địa chỉ vùng nhớ cũ; v1: Trả về STATUS_ERR_ALLOC</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TC-M2-06</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>REQ-4</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Bảo toàn địa chỉ và quyền sở hữu vùng nhớ cũ khi OOM (Ownership Retention)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>realloc trả về NULL</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>So sánh địa chỉ con trỏ items trước và sau khi realloc thất bại</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>v0: Con trỏ gốc bị ghi đè thành NULL; v1: Địa chỉ cũ được bảo toàn 100%</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TC-M2-07</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>REQ-4</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Bảo toàn tính toàn vẹn của dữ liệu đã có khi OOM (Data Integrity on Failure)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Danh sách chứa sẵn 16 mặt hàng ban đầu</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sau khi mở rộng thất bại, duyệt đọc lại 16 mặt hàng cũ</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>v0: Crash bộ nhớ do con trỏ bị NULL hóa; v1: 16 mặt hàng cũ còn nguyên vẹn</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TC-M2-08</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>REQ-4</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Kiểm toán rò rỉ bộ nhớ bằng LeakSanitizer (LSan Memory Leak Audit)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Biên dịch bản v0 và v1 với flag -fsanitize=leak</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Chạy kịch bản nhập kho OOM trên bản v0 và v1
+Kiểm tra log của LeakSanitizer</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>v0: LSan bắt lỗi leaked 16 blocks (CWE-401); v1: LSan báo 0 byte leaked</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TC-M2-09</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>REQ-5</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Con trỏ mượn bị vô hiệu hóa sau khi mảng động dời địa chỉ (Dangling Pointer on Resize)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Lưu con trỏ mượn p = find_product_by_id(&amp;list, "P0001")</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Gọi add_product kích hoạt realloc sang địa chỉ RAM mới
+Đọc dữ liệu qua con trỏ p ban đầu</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>v0: p trỏ vào vùng nhớ cũ đã bị OS thu hồi; v1: Cảnh báo Borrowed Pointer Invalidation</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TC-M2-10</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>REQ-5</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Đọc con trỏ sau khi free phiên kho (Use-After-Free Audit)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Hàm cleanup_and_read_uaf_v0 giải phóng struct nhưng vẫn return *ptr</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Gọi hàm giải phóng tài nguyên phiên kho
+Thực hiện đọc/ghi vào con trỏ vừa giải phóng</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>v0: Đọc dữ liệu rác/vùng nhớ tự do (CWE-416); v1: Triệt tiêu hoàn toàn vì con trỏ đã set NULL</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TC-M2-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>REQ-5</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Bắt lỗi Heap-Use-After-Free bằng AddressSanitizer (ASan Crash Trigger)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Biên dịch mã nguồn với flag -fsanitize=address</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Thực thi test_sim001_heap trên bản v0
+Ghi nhận crash log do ASan sinh ra</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>v0: ASan sinh log crash: ERROR: AddressSanitizer: heap-use-after-free on address; v1: 0 crash</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TC-M2-12</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>REQ-5</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Phòng thủ giải phóng hai lần trên cùng một con trỏ (Double-Free Defense)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Gọi product_list_free(&amp;list) liên tiếp 2 lần</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Thực hiện lệnh free(list-&gt;items) lần 1
+Thực hiện tiếp lệnh free(list-&gt;items) lần 2</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>v0: Crash OS double free or corruption (CWE-415); v1: Lần 2 gặp con trỏ NULL nên bỏ qua an toàn</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TC-M2-13</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>REQ-3</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Kiểm toán bất biến an toàn bộ nhớ (Safety Invariant: count &lt;= capacity)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Chạy qua 50 lần thêm/xóa ngẫu nhiên</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Kiểm tra điều kiện list.count &lt;= list.capacity tại mọi thời điểm</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Bất biến an toàn luôn được duy trì 100% trong suốt vòng đời mảng động</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TC-M2-14</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>REQ-1, REQ-2, REQ-3, REQ-4, REQ-5</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Kiểm thử hồi quy đối chứng toàn diện pytest (Regression Verification Suite)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Bộ test pytest test_verify_v0_cases_on_v1.py</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Chạy toàn bộ test cases trên bản lỗi v0
+Chạy lại toàn bộ test cases trên bản vá v1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>v0: Phát hiện đầy đủ lỗi CWE-190, CWE-401, CWE-416; v1: 100% PASSED (Xanh toàn bộ)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TC-M3-01</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>REQ-1, REQ-4</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Cộng dồn số lượng hàng hóa gây tràn số nguyên có dấu 32-bit</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>old_stock = 2.147.483.640, added_quantity = 100</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Chạy check_satisfiability() trên stock_addition_overflow (Chương 3 Z3)
+Kiểm tra AG(!integer_overflow) trên luồng M3-v0</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>v0: VI PHẠM (CWE-190 Signed Integer Overflow), kết quả lật âm; v1: ĐÚNG (chặn trước khi cộng)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TC-M3-02</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>REQ-3, REQ-5</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Từ chối số lượng nhập hàng là số âm</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>added_quantity = -50</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Kiểm tra AG(!negative_input) trên luồng M3-v0
+Kiểm tra lại trên luồng M3-v1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>v0: VI PHẠM (nhận số âm); v1: ĐÚNG (rào chắn từ chối ngay lập tức)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2798,225 +3414,190 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>ingest_raw_line</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>buffer_copy</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>dst, cap, raw_line</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>raw_line</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>32</v>
       </c>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>H1 — Nạp chuỗi an toàn phòng thủ (M1 Thọ)</t>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>H1 — Nạp chuỗi an toàn phòng thủ strncpy/giới hạn 32 byte (M1 Thọ)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>get_token_field</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>array_read</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>token_offsets, token_count, field_idx</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>H2 — Đọc token an toàn phòng thủ (M1 Thọ)</t>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>arithmetic</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>token_count, field_idx</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>H2 — Kiểm tra biên token an toàn [0, token_count-1] (M1 Thọ)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>expand_stock_items</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>alloc_release</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>list, new_capacity</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" t="n">
         <v>16</v>
       </c>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>H3 — realloc an toàn bảo toàn vùng nhớ qua tmp (M2 Trang)</t>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>H3 — Cấp phát Heap và giải phóng an toàn free(buf) (M2 Trang)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>release_stock_items</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>alloc_release</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>list</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" t="n">
         <v>16</v>
       </c>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H6 — free() và gán con trỏ = NULL (M2 Trang)</t>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>H6 — free() xong gán buf = NULL triệt tiêu UAF (M2 Trang)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>update_stock_quantity</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>arithmetic</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>current_stock, added_quantity</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>H4 — Cộng tồn kho an toàn phòng thủ (M3 Đô)</t>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>H4 — Cộng dồn tồn kho có rào chắn chặn tràn INT_MAX (M3 Đô)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>scale_product_price</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>arithmetic</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>base_price, rate</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="n"/>
-      <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>H5 — Nhân tỉ giá an toàn phòng thủ (M3 Đô)</t>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>H5 — Nhân tỉ giá có rào chắn chặn tràn int32 (M3 Đô)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>calc_batch_capacity</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>divide</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>total_items, batch_size</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
-      <c r="G8" s="2" t="n"/>
-      <c r="H8" s="2" t="n"/>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>H3 — Kiểm tra batch_size &gt; 0 trước khi chia</t>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>H3 — Kiểm tra batch_size != 0 trước khi chia (M2 Trang)</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3069,110 +3650,164 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>buffer_capacity_check</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>cap, input_len</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>cap == 32 and input_len &lt; cap</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>input_len - cap</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>H1 — Rào chắn kiểm tra độ dài input_len &lt; 32 byte ngăn chặn tràn stack (M1 Thọ - Z3 UNSAT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>token_index_check</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>token_count, field_idx</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>token_count &gt; 0 and (field_idx &lt; 0 or field_idx &gt;= token_count)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>field_idx - token_count</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>H2 — Rào chắn từ chối chỉ số âm hoặc vượt trần (M1 Thọ - Z3 UNSAT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>heap_alloc_bytes</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>new_capacity, item_size</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>new_capacity &gt;= 1 and item_size == 48 and new_capacity * item_size &gt; 2147483647</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>new_capacity * item_size</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>H3 — Rào chắn MAX_SAFE_CAPACITY ngăn chặn tràn Heap (M2 Trang - Z3 UNSAT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>stock_addition_overflow</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>current_stock, added_quantity</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>current_stock &gt;= 0 and added_quantity &gt;= 1 and current_stock + added_quantity &gt; 2147483647</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>current_stock + added_quantity</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>H4 — rào chắn ngăn chặn hoàn toàn (Z3 UNSAT trên v1 - M3 Đô)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>heap_alloc_bytes</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>new_capacity, item_size</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>new_capacity &gt;= 1 and item_size == 48 and new_capacity * item_size &gt; 2147483647</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>new_capacity * item_size</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>H3 — rào chắn giới hạn MAX_SAFE_CAPACITY (Z3 UNSAT - M2 Trang)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>old_stock, added_quantity</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>old_stock &gt;= 0 and old_stock &lt;= 2147483647 and added_quantity &gt;= 1 and added_quantity &lt;= 2147483647 and old_stock + added_quantity &gt; 2147483647</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>old_stock + added_quantity</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>H4 — Rào chắn INT_MAX - added_quantity từ chối trước khi cộng (M3 Đô - Z3 UNSAT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>negative_quantity_check</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>added_quantity</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>added_quantity &lt; 0</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>added_quantity</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>H4 — Rào chắn từ chối số lượng nhập âm ngay khi nhận (M3 Đô - Z3 UNSAT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>price_multiplication_overflow</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>base_price, rate</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>base_price &gt; 0 and rate &gt; 1 and base_price * rate &gt; 2147483647</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>base_price * rate</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>H5 — rào chắn kiểm tra trần nhân (Z3 UNSAT - M3 Đô)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>negative_quantity_check</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>added_quantity</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>added_quantity &lt; 0</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>added_quantity</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>H4 — từ chối số âm trước khi xử lý (Z3 UNSAT - M3 Đô)</t>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>H5 — Rào chắn kiểm tra trần nhân giá x tỉ giá (M3 Đô - Z3 UNSAT)</t>
         </is>
       </c>
     </row>
